--- a/data/hex_xlsx/BITTI.HE.xlsx
+++ b/data/hex_xlsx/BITTI.HE.xlsx
@@ -3456,14 +3456,38 @@
       <c r="P36" s="17">
         <v>66.09</v>
       </c>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
+      <c r="Q36" s="17">
+        <f t="shared" ref="Q36:X36" si="1">Q37+Q38</f>
+        <v>68.25</v>
+      </c>
+      <c r="R36" s="17">
+        <f t="shared" si="1"/>
+        <v>84.78</v>
+      </c>
+      <c r="S36" s="17">
+        <f t="shared" si="1"/>
+        <v>134.78</v>
+      </c>
+      <c r="T36" s="17">
+        <f t="shared" si="1"/>
+        <v>127.5</v>
+      </c>
+      <c r="U36" s="17">
+        <f t="shared" si="1"/>
+        <v>66.25</v>
+      </c>
+      <c r="V36" s="17">
+        <f t="shared" si="1"/>
+        <v>77.93</v>
+      </c>
+      <c r="W36" s="17">
+        <f t="shared" si="1"/>
+        <v>96.17</v>
+      </c>
+      <c r="X36" s="17">
+        <f t="shared" si="1"/>
+        <v>4.11</v>
+      </c>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
